--- a/src/test/resources/excel/menuEmpleador/datosMenuEmpleador.xlsx
+++ b/src/test/resources/excel/menuEmpleador/datosMenuEmpleador.xlsx
@@ -1,27 +1,45 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="28025"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\User\Documents\automatizacion\portal Famisanar\src\test\resources\excel\menuEmpleador\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3D50B06-A28A-43C8-B63E-A6EE7480808C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="60" windowWidth="20055" windowHeight="7950" tabRatio="851" activeTab="1"/>
+    <workbookView minimized="1" xWindow="30" yWindow="30" windowWidth="20460" windowHeight="11490" tabRatio="851" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Login" sheetId="4" r:id="rId1"/>
     <sheet name="menusEmpleador" sheetId="6" r:id="rId2"/>
-    <sheet name="grupoFamiliar" sheetId="7" r:id="rId3"/>
-    <sheet name="documentosPendientesAfiliado" sheetId="8" r:id="rId4"/>
-    <sheet name="afiliadosCancelados" sheetId="9" r:id="rId5"/>
-    <sheet name="certificacionDePagos" sheetId="10" r:id="rId6"/>
-    <sheet name="reporteLicencia" sheetId="5" r:id="rId7"/>
-    <sheet name="menuServicioAlCliente" sheetId="1" r:id="rId8"/>
+    <sheet name="documentosPendientesAfiliado" sheetId="8" r:id="rId3"/>
+    <sheet name="afiliadosCancelados" sheetId="9" r:id="rId4"/>
+    <sheet name="certificacionDePagos" sheetId="10" r:id="rId5"/>
+    <sheet name="reporteLicencia" sheetId="5" r:id="rId6"/>
+    <sheet name="menuServicioAlCliente" sheetId="1" r:id="rId7"/>
   </sheets>
-  <calcPr calcId="124519"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="214" uniqueCount="107">
   <si>
     <t>acastillo@basewarnet.com</t>
   </si>
@@ -341,15 +359,75 @@
   <si>
     <t>MARIO FIDEL RODRIGUEZ NARVAE</t>
   </si>
+  <si>
+    <t>52271564</t>
+  </si>
+  <si>
+    <t>Documentos Pendientes Por Afiliado</t>
+  </si>
+  <si>
+    <t>Dia inicio</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">El usuario </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color rgb="FFFF0000"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>debe existir en la BD</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">Mes inicio </t>
+  </si>
+  <si>
+    <t>enero</t>
+  </si>
+  <si>
+    <t>Año inicio</t>
+  </si>
+  <si>
+    <t>2024</t>
+  </si>
+  <si>
+    <t>Dia fin</t>
+  </si>
+  <si>
+    <t>Mes fin</t>
+  </si>
+  <si>
+    <t>febrero</t>
+  </si>
+  <si>
+    <t>Año fin</t>
+  </si>
+  <si>
+    <t>Dato a Modificar</t>
+  </si>
+  <si>
+    <t>Afiliados Cancelados</t>
+  </si>
+  <si>
+    <t>Certificacion Pagos</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
-  <fonts count="16">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -671,7 +749,7 @@
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="66">
+  <cellXfs count="69">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
@@ -683,15 +761,14 @@
     <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="3" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="9" xfId="3" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="3" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="3" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="11" xfId="3" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -701,22 +778,20 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="12" xfId="3" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="9" fillId="0" borderId="9" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1"/>
     <xf numFmtId="0" fontId="7" fillId="2" borderId="8" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="3" fillId="0" borderId="6" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="8" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="11" xfId="3" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="9" xfId="3" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="13" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="14" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -725,12 +800,11 @@
     <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="4" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="49" fontId="4" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -742,50 +816,63 @@
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="3" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="3" applyBorder="1"/>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="14" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="6" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="5" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="4" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="14" xfId="3" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="6" xfId="3" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="8" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="3" applyBorder="1"/>
-    <xf numFmtId="49" fontId="3" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="4" fillId="4" borderId="14" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="12" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="14" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="7" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="4" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="4" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="10" xfId="3" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="10" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="3" applyBorder="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="49" fontId="3" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="20% - Énfasis1" xfId="3" builtinId="30"/>
@@ -794,22 +881,61 @@
     <cellStyle name="Millares" xfId="1" builtinId="3"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="9">
+  <dxfs count="23">
     <dxf>
-      <border outline="0">
-        <bottom style="thin">
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
           <color indexed="64"/>
-        </bottom>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
     </dxf>
     <dxf>
       <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <bottom style="thin">
+        <top style="thin">
           <color indexed="64"/>
-        </bottom>
+        </top>
       </border>
     </dxf>
     <dxf>
@@ -826,25 +952,65 @@
         <sz val="10"/>
         <color theme="0"/>
         <name val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
-      <border outline="0">
-        <bottom style="thin">
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <border diagonalUp="0" diagonalDown="0">
+        <left/>
+        <right style="thin">
           <color indexed="64"/>
-        </bottom>
+        </right>
+        <top/>
+        <bottom/>
+        <vertical/>
+        <horizontal/>
       </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="0"/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="1"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
     </dxf>
     <dxf>
       <border outline="0">
         <left style="thin">
           <color indexed="64"/>
         </left>
-        <bottom style="thin">
+        <top style="thin">
           <color indexed="64"/>
-        </bottom>
+        </top>
       </border>
     </dxf>
     <dxf>
@@ -861,9 +1027,10 @@
         <sz val="10"/>
         <color theme="0"/>
         <name val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
     <dxf>
       <border outline="0">
@@ -898,13 +1065,153 @@
         <name val="Calibri"/>
         <scheme val="minor"/>
       </font>
-      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" indent="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" mergeCell="0" readingOrder="0"/>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <left style="thin">
+          <color indexed="64"/>
+        </left>
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <border outline="0">
+        <bottom style="thin">
+          <color indexed="64"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b/>
+        <i val="0"/>
+        <strike val="0"/>
+        <condense val="0"/>
+        <extend val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="10"/>
+        <color theme="0"/>
+        <name val="Calibri"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="bottom" textRotation="0" wrapText="0" relativeIndent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="3" defaultTableStyle="Estilo de tabla 1" defaultPivotStyle="PivotStyleLight16">
-    <tableStyle name="Estilo de tabla 1" pivot="0" count="0"/>
-    <tableStyle name="Estilo de tabla dinámica 1" table="0" count="0"/>
-    <tableStyle name="Estilo de tabla dinámica 2" table="0" count="0"/>
+    <tableStyle name="Estilo de tabla 1" pivot="0" count="0" xr9:uid="{00000000-0011-0000-FFFF-FFFF00000000}"/>
+    <tableStyle name="Estilo de tabla dinámica 1" table="0" count="0" xr9:uid="{00000000-0011-0000-FFFF-FFFF01000000}"/>
+    <tableStyle name="Estilo de tabla dinámica 2" table="0" count="0" xr9:uid="{00000000-0011-0000-FFFF-FFFF02000000}"/>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -918,45 +1225,93 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="login" displayName="login" ref="A1:C4" totalsRowShown="0" headerRowDxfId="8" headerRowBorderDxfId="7" tableBorderDxfId="6" headerRowCellStyle="Énfasis1">
-  <autoFilter ref="A1:C4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{00000000-000C-0000-FFFF-FFFF00000000}" name="login" displayName="login" ref="A1:C4" totalsRowShown="0" headerRowDxfId="22" headerRowBorderDxfId="21" tableBorderDxfId="20" headerRowCellStyle="Énfasis1">
+  <autoFilter ref="A1:C4" xr:uid="{00000000-0009-0000-0100-000002000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="Inicio de Sesión Portal"/>
-    <tableColumn id="2" name="Columna1"/>
-    <tableColumn id="3" name="Columna2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="Inicio de Sesión Portal"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Columna1"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Columna2"/>
   </tableColumns>
   <tableStyleInfo name="Estilo de tabla 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="login2" displayName="login2" ref="A1:C4" totalsRowShown="0" headerRowDxfId="5" headerRowBorderDxfId="3" tableBorderDxfId="4" headerRowCellStyle="Énfasis1">
-  <autoFilter ref="A1:C4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="3" xr:uid="{00000000-000C-0000-FFFF-FFFF02000000}" name="login24" displayName="login24" ref="E1:G4" totalsRowShown="0" headerRowDxfId="19" headerRowBorderDxfId="18" tableBorderDxfId="17" headerRowCellStyle="Énfasis1">
+  <autoFilter ref="E1:G4" xr:uid="{00000000-0009-0000-0100-000003000000}"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="Inicio de Sesión Portal"/>
-    <tableColumn id="2" name="Columna1"/>
-    <tableColumn id="3" name="Columna2"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0200-000001000000}" name="Actualizar Informacion Empleador"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0200-000002000000}" name="Columna1"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0200-000003000000}" name="Columna2"/>
   </tableColumns>
   <tableStyleInfo name="Estilo de tabla 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="login24" displayName="login24" ref="E1:G4" totalsRowShown="0" headerRowDxfId="2" headerRowBorderDxfId="0" tableBorderDxfId="1" headerRowCellStyle="Énfasis1">
-  <autoFilter ref="E1:G4"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{F4B710A6-3B16-4EF4-B4B8-51E7EEA03C4D}" name="login245" displayName="login245" ref="I1:K4" totalsRowShown="0" headerRowDxfId="16" headerRowBorderDxfId="15" tableBorderDxfId="14" headerRowCellStyle="Énfasis1">
+  <autoFilter ref="I1:K4" xr:uid="{F4B710A6-3B16-4EF4-B4B8-51E7EEA03C4D}"/>
   <tableColumns count="3">
-    <tableColumn id="1" name="Actualizar Informacion Empleador"/>
-    <tableColumn id="2" name="Columna1"/>
-    <tableColumn id="3" name="Columna2"/>
+    <tableColumn id="1" xr3:uid="{80CF33BC-F233-4CC1-8EC7-2F576036757E}" name="Grupo Familiar"/>
+    <tableColumn id="2" xr3:uid="{79F2863F-23D0-43EF-B296-DA9501C576C4}" name="Columna1"/>
+    <tableColumn id="3" xr3:uid="{6B660B06-5586-45E6-A31A-A5817D79F90F}" name="Columna2"/>
+  </tableColumns>
+  <tableStyleInfo name="Estilo de tabla 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="5" xr:uid="{CFB7DF34-07F6-40BA-8855-3CD59603FD1F}" name="login2456" displayName="login2456" ref="M1:O4" totalsRowShown="0" headerRowDxfId="13" headerRowBorderDxfId="12" tableBorderDxfId="11" headerRowCellStyle="Énfasis1">
+  <autoFilter ref="M1:O4" xr:uid="{CFB7DF34-07F6-40BA-8855-3CD59603FD1F}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{664F78C7-EE55-47D3-AEDF-6D5B49E08BAB}" name="Documentos Pendientes Por Afiliado"/>
+    <tableColumn id="2" xr3:uid="{1FE1443F-576F-4818-A0E9-886225F446FE}" name="Columna1"/>
+    <tableColumn id="3" xr3:uid="{A98927E9-5D81-4526-A1E1-D93994EAE178}" name="Columna2"/>
+  </tableColumns>
+  <tableStyleInfo name="Estilo de tabla 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table5.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="1" xr:uid="{00000000-000C-0000-FFFF-FFFF01000000}" name="login2" displayName="login2" ref="A1:C4" totalsRowShown="0" headerRowDxfId="10" headerRowBorderDxfId="9" tableBorderDxfId="8" headerRowCellStyle="Énfasis1">
+  <autoFilter ref="A1:C4" xr:uid="{00000000-0009-0000-0100-000001000000}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0100-000001000000}" name="Inicio de Sesión Portal"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0100-000002000000}" name="Columna1"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0100-000003000000}" name="Columna2"/>
+  </tableColumns>
+  <tableStyleInfo name="Estilo de tabla 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table6.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="6" xr:uid="{73003D35-2594-4723-8B63-1D66E21A85C0}" name="Tabla74" displayName="Tabla74" ref="Q1:S8" totalsRowShown="0" headerRowDxfId="7" tableBorderDxfId="6" headerRowCellStyle="Énfasis1">
+  <autoFilter ref="Q1:S8" xr:uid="{73003D35-2594-4723-8B63-1D66E21A85C0}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{F59432C1-05AC-4FCC-ACB1-DCF8C48E2E79}" name="Afiliados Cancelados" dataCellStyle="20% - Énfasis1"/>
+    <tableColumn id="2" xr3:uid="{C9D9F571-A461-4EF3-935B-9796EF1A79CD}" name="Columna1" dataDxfId="5"/>
+    <tableColumn id="3" xr3:uid="{DE6A8886-2D88-42D1-994A-BBCA6F2A89A1}" name="Columna2" dataDxfId="4"/>
+  </tableColumns>
+  <tableStyleInfo name="Estilo de tabla 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
+</file>
+
+<file path=xl/tables/table7.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="7" xr:uid="{05AE36FF-DE3F-426E-9520-A0BEB835D061}" name="Tabla748" displayName="Tabla748" ref="U1:W8" totalsRowShown="0" headerRowDxfId="3" tableBorderDxfId="2" headerRowCellStyle="Énfasis1">
+  <autoFilter ref="U1:W8" xr:uid="{05AE36FF-DE3F-426E-9520-A0BEB835D061}"/>
+  <tableColumns count="3">
+    <tableColumn id="1" xr3:uid="{C3C65051-246E-4B2E-A15D-BE1E12A318D5}" name="Certificacion Pagos" dataCellStyle="20% - Énfasis1"/>
+    <tableColumn id="2" xr3:uid="{28663EA5-6383-494B-9886-07F6AD0E41F4}" name="Columna1" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{5AAFE680-4EF5-4BD7-B5C2-1FC152FC3A92}" name="Columna2" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="Estilo de tabla 1" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -994,7 +1349,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -1028,6 +1383,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -1062,9 +1418,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -1237,28 +1594,28 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="22.7109375" customWidth="1"/>
     <col min="2" max="2" width="19.7109375" customWidth="1"/>
     <col min="3" max="3" width="25.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="49" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="49" t="s">
+      <c r="B1" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="C1" s="49" t="s">
+      <c r="C1" s="44" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="2" spans="1:3">
-      <c r="A2" s="52" t="s">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A2" s="46" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -1268,25 +1625,25 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="53" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="54" t="s">
+      <c r="B3" s="15" t="s">
         <v>86</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="55" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="56" t="s">
+      <c r="B4" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="C4" s="50"/>
+      <c r="C4" s="45"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1298,9 +1655,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
+  <dimension ref="A1:W8"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="24.140625" customWidth="1"/>
     <col min="2" max="2" width="22.7109375" customWidth="1"/>
@@ -1309,30 +1666,76 @@
     <col min="5" max="5" width="40.7109375" customWidth="1"/>
     <col min="6" max="6" width="37.140625" customWidth="1"/>
     <col min="7" max="7" width="33.42578125" customWidth="1"/>
+    <col min="9" max="9" width="27.28515625" customWidth="1"/>
+    <col min="10" max="10" width="25.5703125" customWidth="1"/>
+    <col min="11" max="11" width="28.140625" customWidth="1"/>
+    <col min="13" max="13" width="48.5703125" customWidth="1"/>
+    <col min="14" max="14" width="22.85546875" customWidth="1"/>
+    <col min="15" max="15" width="24.7109375" customWidth="1"/>
+    <col min="17" max="17" width="29.85546875" customWidth="1"/>
+    <col min="18" max="18" width="18.7109375" customWidth="1"/>
+    <col min="19" max="19" width="20.42578125" customWidth="1"/>
+    <col min="21" max="21" width="28.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
-      <c r="A1" s="51" t="s">
+    <row r="1" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A1" s="44" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="51" t="s">
+      <c r="B1" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="C1" s="51" t="s">
+      <c r="C1" s="44" t="s">
         <v>88</v>
       </c>
-      <c r="E1" s="51" t="s">
+      <c r="E1" s="44" t="s">
         <v>89</v>
       </c>
-      <c r="F1" s="51" t="s">
+      <c r="F1" s="44" t="s">
         <v>87</v>
       </c>
-      <c r="G1" s="51" t="s">
+      <c r="G1" s="44" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="52" t="s">
+      <c r="I1" s="44" t="s">
+        <v>54</v>
+      </c>
+      <c r="J1" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="K1" s="44" t="s">
+        <v>88</v>
+      </c>
+      <c r="M1" s="44" t="s">
+        <v>92</v>
+      </c>
+      <c r="N1" s="44" t="s">
+        <v>87</v>
+      </c>
+      <c r="O1" s="44" t="s">
+        <v>88</v>
+      </c>
+      <c r="Q1" s="62" t="s">
+        <v>105</v>
+      </c>
+      <c r="R1" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="S1" s="62" t="s">
+        <v>88</v>
+      </c>
+      <c r="U1" s="62" t="s">
+        <v>106</v>
+      </c>
+      <c r="V1" s="62" t="s">
+        <v>87</v>
+      </c>
+      <c r="W1" s="62" t="s">
+        <v>88</v>
+      </c>
+    </row>
+    <row r="2" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A2" s="46" t="s">
         <v>11</v>
       </c>
       <c r="B2" s="3" t="s">
@@ -1341,7 +1744,7 @@
       <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="52" t="s">
+      <c r="E2" s="46" t="s">
         <v>11</v>
       </c>
       <c r="F2" s="3" t="s">
@@ -1350,205 +1753,308 @@
       <c r="G2" s="3" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="53" t="s">
+      <c r="I2" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="J2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="K2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="M2" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="N2" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="O2" s="3" t="s">
+        <v>9</v>
+      </c>
+      <c r="Q2" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="R2" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="S2" s="29" t="s">
+        <v>9</v>
+      </c>
+      <c r="U2" s="50" t="s">
+        <v>11</v>
+      </c>
+      <c r="V2" s="29" t="s">
+        <v>10</v>
+      </c>
+      <c r="W2" s="29" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="3" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A3" s="47" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="54" t="s">
+      <c r="B3" s="15" t="s">
         <v>86</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="53" t="s">
+      <c r="E3" s="47" t="s">
         <v>69</v>
       </c>
-      <c r="F3" s="54" t="s">
+      <c r="F3" s="15" t="s">
         <v>90</v>
       </c>
       <c r="G3" s="7" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="55" t="s">
+      <c r="I3" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="J3" s="49" t="s">
+        <v>2</v>
+      </c>
+      <c r="K3" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="M3" s="52" t="s">
+        <v>73</v>
+      </c>
+      <c r="N3" s="49" t="s">
+        <v>2</v>
+      </c>
+      <c r="O3" s="7" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q3" s="63" t="s">
+        <v>93</v>
+      </c>
+      <c r="R3" s="64" t="s">
+        <v>94</v>
+      </c>
+      <c r="S3" s="9" t="s">
+        <v>95</v>
+      </c>
+      <c r="U3" s="63" t="s">
+        <v>93</v>
+      </c>
+      <c r="V3" s="64" t="s">
+        <v>94</v>
+      </c>
+      <c r="W3" s="9" t="s">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="4" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="A4" s="48" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="56" t="s">
+      <c r="B4" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="C4" s="50"/>
-      <c r="E4" s="55"/>
-      <c r="F4" s="56"/>
-      <c r="G4" s="50"/>
-    </row>
-    <row r="5" spans="1:7">
-      <c r="B5" s="59"/>
-      <c r="C5" s="59"/>
-      <c r="D5" s="37"/>
-    </row>
-    <row r="6" spans="1:7">
-      <c r="B6" s="37"/>
-      <c r="C6" s="38"/>
-      <c r="D6" s="60"/>
-    </row>
-    <row r="7" spans="1:7">
-      <c r="B7" s="37"/>
-      <c r="C7" s="38"/>
-      <c r="D7" s="60"/>
+      <c r="C4" s="45"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="26"/>
+      <c r="G4" s="45"/>
+      <c r="I4" s="51" t="s">
+        <v>71</v>
+      </c>
+      <c r="J4" s="49" t="s">
+        <v>91</v>
+      </c>
+      <c r="K4" s="45"/>
+      <c r="M4" s="51" t="s">
+        <v>71</v>
+      </c>
+      <c r="N4" s="49" t="s">
+        <v>91</v>
+      </c>
+      <c r="O4" s="45"/>
+      <c r="Q4" s="65" t="s">
+        <v>96</v>
+      </c>
+      <c r="R4" s="66" t="s">
+        <v>97</v>
+      </c>
+      <c r="S4" s="10"/>
+      <c r="U4" s="65" t="s">
+        <v>96</v>
+      </c>
+      <c r="V4" s="66" t="s">
+        <v>97</v>
+      </c>
+      <c r="W4" s="10"/>
+    </row>
+    <row r="5" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B5" s="53"/>
+      <c r="C5" s="53"/>
+      <c r="D5" s="34"/>
+      <c r="Q5" s="65" t="s">
+        <v>98</v>
+      </c>
+      <c r="R5" s="66" t="s">
+        <v>99</v>
+      </c>
+      <c r="S5" s="2"/>
+      <c r="U5" s="65" t="s">
+        <v>98</v>
+      </c>
+      <c r="V5" s="66" t="s">
+        <v>99</v>
+      </c>
+      <c r="W5" s="2"/>
+    </row>
+    <row r="6" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B6" s="34"/>
+      <c r="C6" s="35"/>
+      <c r="D6" s="54"/>
+      <c r="Q6" s="63" t="s">
+        <v>100</v>
+      </c>
+      <c r="R6" s="66" t="s">
+        <v>94</v>
+      </c>
+      <c r="S6" s="2"/>
+      <c r="U6" s="63" t="s">
+        <v>100</v>
+      </c>
+      <c r="V6" s="66" t="s">
+        <v>94</v>
+      </c>
+      <c r="W6" s="2"/>
+    </row>
+    <row r="7" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="B7" s="34"/>
+      <c r="C7" s="35"/>
+      <c r="D7" s="54"/>
+      <c r="Q7" s="65" t="s">
+        <v>101</v>
+      </c>
+      <c r="R7" s="66" t="s">
+        <v>102</v>
+      </c>
+      <c r="S7" s="2"/>
+      <c r="U7" s="65" t="s">
+        <v>101</v>
+      </c>
+      <c r="V7" s="66" t="s">
+        <v>102</v>
+      </c>
+      <c r="W7" s="2"/>
+    </row>
+    <row r="8" spans="1:23" x14ac:dyDescent="0.25">
+      <c r="Q8" s="65" t="s">
+        <v>103</v>
+      </c>
+      <c r="R8" s="67" t="s">
+        <v>99</v>
+      </c>
+      <c r="S8" s="68" t="s">
+        <v>104</v>
+      </c>
+      <c r="U8" s="65" t="s">
+        <v>103</v>
+      </c>
+      <c r="V8" s="67" t="s">
+        <v>99</v>
+      </c>
+      <c r="W8" s="68" t="s">
+        <v>104</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="B5:C5"/>
     <mergeCell ref="D6:D7"/>
   </mergeCells>
-  <dataValidations count="6">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C42 C62">
+  <dataValidations count="7">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C42 C62" xr:uid="{00000000-0002-0000-0100-000000000000}">
       <formula1>"ÁLAMOS,NORTE,SABANA"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C41 C61">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C41 C61" xr:uid="{00000000-0002-0000-0100-000001000000}">
       <formula1>"ZONA BOGOTA"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C39 C46 C59 C66">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C39 C46 C59 C66" xr:uid="{00000000-0002-0000-0100-000002000000}">
       <formula1>"FUSAGASUGA,GIRARDOT,TOCANCIPA"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C38 C45 C58 C65">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C38 C45 C58 C65" xr:uid="{00000000-0002-0000-0100-000003000000}">
       <formula1>"CUNDINAMARCA"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C35 C55">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C35 C55" xr:uid="{00000000-0002-0000-0100-000004000000}">
       <formula1>"EL NOGAL,EL MUELLE,EL LAUREL,"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C34 C54">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C34 C54" xr:uid="{00000000-0002-0000-0100-000005000000}">
       <formula1>"Rural,Urbana"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="J3 N3" xr:uid="{00000000-0002-0000-0200-000000000000}">
+      <formula1>"TI,CC,CE"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <tableParts count="2">
-    <tablePart r:id="rId1"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <tableParts count="6">
     <tablePart r:id="rId2"/>
+    <tablePart r:id="rId3"/>
+    <tablePart r:id="rId4"/>
+    <tablePart r:id="rId5"/>
+    <tablePart r:id="rId6"/>
+    <tablePart r:id="rId7"/>
   </tableParts>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B3:D7"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="B3:D6"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="11.42578125" style="42"/>
-    <col min="2" max="2" width="21.85546875" style="42" customWidth="1"/>
-    <col min="3" max="3" width="29.7109375" style="42" customWidth="1"/>
-    <col min="4" max="4" width="73.85546875" style="42" customWidth="1"/>
-    <col min="5" max="16384" width="11.42578125" style="42"/>
+    <col min="2" max="3" width="27.42578125" customWidth="1"/>
+    <col min="4" max="4" width="71" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:4">
-      <c r="B3" s="57" t="s">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B3" s="55" t="s">
         <v>75</v>
       </c>
-      <c r="C3" s="58"/>
-      <c r="D3" s="43" t="s">
+      <c r="C3" s="56"/>
+      <c r="D3" s="39" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="4" spans="2:4">
-      <c r="B4" s="45" t="s">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B4" s="41" t="s">
         <v>73</v>
       </c>
-      <c r="C4" s="40" t="s">
+      <c r="C4" s="37" t="s">
         <v>2</v>
       </c>
-      <c r="D4" s="39" t="s">
+      <c r="D4" s="36" t="s">
         <v>72</v>
       </c>
     </row>
-    <row r="5" spans="2:4">
-      <c r="B5" s="45" t="s">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B5" s="41" t="s">
         <v>71</v>
       </c>
-      <c r="C5" s="40" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="39" t="s">
+      <c r="C5" s="37" t="s">
+        <v>76</v>
+      </c>
+      <c r="D5" s="36" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="6" spans="2:4">
-      <c r="B6" s="44"/>
-      <c r="C6" s="41"/>
-      <c r="D6" s="41"/>
-    </row>
-    <row r="7" spans="2:4">
-      <c r="B7" s="41"/>
-      <c r="C7" s="41"/>
-      <c r="D7" s="41"/>
+    <row r="6" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B6" s="40"/>
+      <c r="C6" s="38"/>
+      <c r="D6" s="38"/>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B3:C3"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4">
-      <formula1>"TI,CC,CE"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="200" verticalDpi="200" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="B3:D6"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
-  <cols>
-    <col min="2" max="3" width="27.42578125" customWidth="1"/>
-    <col min="4" max="4" width="71" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="3" spans="2:4">
-      <c r="B3" s="57" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3" s="58"/>
-      <c r="D3" s="43" t="s">
-        <v>74</v>
-      </c>
-    </row>
-    <row r="4" spans="2:4">
-      <c r="B4" s="45" t="s">
-        <v>73</v>
-      </c>
-      <c r="C4" s="40" t="s">
-        <v>2</v>
-      </c>
-      <c r="D4" s="39" t="s">
-        <v>72</v>
-      </c>
-    </row>
-    <row r="5" spans="2:4">
-      <c r="B5" s="45" t="s">
-        <v>71</v>
-      </c>
-      <c r="C5" s="40" t="s">
-        <v>76</v>
-      </c>
-      <c r="D5" s="39" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="6" spans="2:4">
-      <c r="B6" s="44"/>
-      <c r="C6" s="41"/>
-      <c r="D6" s="41"/>
-    </row>
-  </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="B3:C3"/>
-  </mergeCells>
-  <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C4" xr:uid="{00000000-0002-0000-0300-000000000000}">
       <formula1>"TI,CC,CE"</formula1>
     </dataValidation>
   </dataValidations>
@@ -1556,44 +2062,44 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="B3:D5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="35.28515625" customWidth="1"/>
     <col min="3" max="3" width="37.42578125" customWidth="1"/>
     <col min="4" max="4" width="48.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:4" ht="19.5" customHeight="1">
-      <c r="B3" s="61" t="s">
+    <row r="3" spans="2:4" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B3" s="57" t="s">
         <v>82</v>
       </c>
-      <c r="C3" s="61"/>
-      <c r="D3" s="47" t="s">
+      <c r="C3" s="57"/>
+      <c r="D3" s="43" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="4" spans="2:4" ht="18.75" customHeight="1">
-      <c r="B4" s="47" t="s">
+    <row r="4" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B4" s="43" t="s">
         <v>81</v>
       </c>
-      <c r="C4" s="40" t="s">
+      <c r="C4" s="37" t="s">
         <v>80</v>
       </c>
-      <c r="D4" s="46" t="s">
+      <c r="D4" s="42" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="5" spans="2:4" ht="18.75" customHeight="1">
-      <c r="B5" s="47" t="s">
+    <row r="5" spans="2:4" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B5" s="43" t="s">
         <v>79</v>
       </c>
-      <c r="C5" s="40" t="s">
+      <c r="C5" s="37" t="s">
         <v>78</v>
       </c>
-      <c r="D5" s="46" t="s">
+      <c r="D5" s="42" t="s">
         <v>77</v>
       </c>
     </row>
@@ -1606,44 +2112,44 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
   <dimension ref="B3:D5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="2" max="2" width="21.140625" customWidth="1"/>
     <col min="3" max="3" width="21.28515625" customWidth="1"/>
     <col min="4" max="4" width="53" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="3" spans="2:4">
-      <c r="B3" s="61" t="s">
+    <row r="3" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B3" s="57" t="s">
         <v>85</v>
       </c>
-      <c r="C3" s="61"/>
-      <c r="D3" s="48" t="s">
+      <c r="C3" s="57"/>
+      <c r="D3" s="43" t="s">
         <v>74</v>
       </c>
     </row>
-    <row r="4" spans="2:4">
-      <c r="B4" s="48" t="s">
+    <row r="4" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B4" s="43" t="s">
         <v>81</v>
       </c>
-      <c r="C4" s="40" t="s">
+      <c r="C4" s="37" t="s">
         <v>84</v>
       </c>
-      <c r="D4" s="46" t="s">
+      <c r="D4" s="42" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="5" spans="2:4">
-      <c r="B5" s="48" t="s">
+    <row r="5" spans="2:4" x14ac:dyDescent="0.25">
+      <c r="B5" s="43" t="s">
         <v>79</v>
       </c>
-      <c r="C5" s="40" t="s">
+      <c r="C5" s="37" t="s">
         <v>83</v>
       </c>
-      <c r="D5" s="46" t="s">
+      <c r="D5" s="42" t="s">
         <v>77</v>
       </c>
     </row>
@@ -1656,24 +2162,24 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
   <dimension ref="A1:C5"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="16.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="20.5703125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="50.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3">
-      <c r="A1" s="62" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1" s="58" t="s">
         <v>65</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-    </row>
-    <row r="2" spans="1:3">
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
@@ -1684,30 +2190,30 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:3">
-      <c r="A3" s="34" t="s">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A3" s="31" t="s">
         <v>59</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="15" t="s">
         <v>62</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="4" spans="1:3">
-      <c r="A4" s="35" t="s">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A4" s="32" t="s">
         <v>61</v>
       </c>
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="C4" s="28" t="s">
+      <c r="C4" s="27" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="5" spans="1:3">
-      <c r="A5" s="36" t="s">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A5" s="33" t="s">
         <v>60</v>
       </c>
       <c r="B5" s="4" t="s">
@@ -1722,17 +2228,17 @@
     <mergeCell ref="A1:C1"/>
   </mergeCells>
   <dataValidations count="1">
-    <dataValidation showInputMessage="1" showErrorMessage="1" sqref="B3"/>
+    <dataValidation showInputMessage="1" showErrorMessage="1" sqref="B3" xr:uid="{00000000-0002-0000-0600-000000000000}"/>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:Q21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75"/>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
+  <dimension ref="A1:O21"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="12.75" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="11.5703125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15.85546875" style="1" bestFit="1" customWidth="1"/>
@@ -1753,29 +2259,29 @@
     <col min="17" max="16384" width="11.42578125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17">
-      <c r="A1" s="62" t="s">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.2">
+      <c r="A1" s="58" t="s">
         <v>5</v>
       </c>
-      <c r="B1" s="63"/>
-      <c r="C1" s="63"/>
-      <c r="E1" s="64" t="s">
+      <c r="B1" s="59"/>
+      <c r="C1" s="59"/>
+      <c r="E1" s="60" t="s">
         <v>12</v>
       </c>
-      <c r="F1" s="65"/>
-      <c r="G1" s="65"/>
-      <c r="I1" s="64" t="s">
+      <c r="F1" s="61"/>
+      <c r="G1" s="61"/>
+      <c r="I1" s="60" t="s">
         <v>15</v>
       </c>
-      <c r="J1" s="65"/>
-      <c r="K1" s="65"/>
-      <c r="M1" s="64" t="s">
+      <c r="J1" s="61"/>
+      <c r="K1" s="61"/>
+      <c r="M1" s="60" t="s">
         <v>17</v>
       </c>
-      <c r="N1" s="65"/>
-      <c r="O1" s="65"/>
-    </row>
-    <row r="2" spans="1:17">
+      <c r="N1" s="61"/>
+      <c r="O1" s="61"/>
+    </row>
+    <row r="2" spans="1:15" x14ac:dyDescent="0.2">
       <c r="A2" s="3" t="s">
         <v>11</v>
       </c>
@@ -1785,13 +2291,13 @@
       <c r="C2" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="30" t="s">
+      <c r="E2" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="F2" s="30" t="s">
+      <c r="F2" s="29" t="s">
         <v>10</v>
       </c>
-      <c r="G2" s="30" t="s">
+      <c r="G2" s="29" t="s">
         <v>9</v>
       </c>
       <c r="I2" s="3" t="s">
@@ -1813,33 +2319,33 @@
         <v>9</v>
       </c>
     </row>
-    <row r="3" spans="1:17" ht="15">
-      <c r="A3" s="12" t="s">
+    <row r="3" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A3" s="11" t="s">
         <v>3</v>
       </c>
-      <c r="B3" s="16" t="s">
+      <c r="B3" s="15" t="s">
         <v>1</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="E3" s="12" t="s">
+      <c r="E3" s="11" t="s">
         <v>6</v>
       </c>
-      <c r="F3" s="31" t="s">
+      <c r="F3" s="30" t="s">
         <v>2</v>
       </c>
       <c r="G3" s="5"/>
-      <c r="I3" s="14" t="s">
+      <c r="I3" s="13" t="s">
         <v>6</v>
       </c>
-      <c r="J3" s="18" t="s">
+      <c r="J3" s="17" t="s">
         <v>2</v>
       </c>
       <c r="K3" s="7" t="s">
         <v>16</v>
       </c>
-      <c r="M3" s="12" t="s">
+      <c r="M3" s="11" t="s">
         <v>6</v>
       </c>
       <c r="N3" s="5" t="s">
@@ -1849,31 +2355,31 @@
         <v>19</v>
       </c>
     </row>
-    <row r="4" spans="1:17" ht="15">
-      <c r="A4" s="13" t="s">
+    <row r="4" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="A4" s="12" t="s">
         <v>4</v>
       </c>
-      <c r="B4" s="17" t="s">
+      <c r="B4" s="16" t="s">
         <v>1</v>
       </c>
       <c r="C4" s="4"/>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="18" t="s">
         <v>7</v>
       </c>
-      <c r="F4" s="32" t="s">
+      <c r="F4" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="G4" s="11" t="s">
+      <c r="G4" s="10" t="s">
         <v>14</v>
       </c>
-      <c r="I4" s="26" t="s">
+      <c r="I4" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="J4" s="27" t="s">
+      <c r="J4" s="26" t="s">
         <v>13</v>
       </c>
-      <c r="K4" s="28"/>
-      <c r="M4" s="13" t="s">
+      <c r="K4" s="27"/>
+      <c r="M4" s="12" t="s">
         <v>7</v>
       </c>
       <c r="N4" s="6" t="s">
@@ -1883,179 +2389,177 @@
         <v>18</v>
       </c>
     </row>
-    <row r="5" spans="1:17" ht="15">
-      <c r="E5" s="13" t="s">
+    <row r="5" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="E5" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="F5" s="33" t="s">
+      <c r="F5" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="G5" s="25" t="s">
+      <c r="G5" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="I5" s="15" t="s">
+      <c r="I5" s="14" t="s">
         <v>52</v>
       </c>
-      <c r="J5" s="29" t="s">
+      <c r="J5" s="28" t="s">
         <v>54</v>
       </c>
-      <c r="K5" s="25"/>
-      <c r="M5" s="12" t="s">
+      <c r="K5" s="24"/>
+      <c r="M5" s="11" t="s">
         <v>20</v>
       </c>
       <c r="N5" s="5" t="s">
         <v>21</v>
       </c>
-      <c r="O5" s="10" t="s">
+      <c r="O5" s="9" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="6" spans="1:17" ht="15">
-      <c r="M6" s="19" t="s">
+    <row r="6" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="M6" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="N6" s="21" t="s">
+      <c r="N6" s="20" t="s">
         <v>51</v>
       </c>
-      <c r="O6" s="11" t="s">
+      <c r="O6" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="P6" s="9"/>
-      <c r="Q6" s="9"/>
-    </row>
-    <row r="7" spans="1:17" ht="15">
+    </row>
+    <row r="7" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="F7" s="1" t="s">
         <v>56</v>
       </c>
       <c r="J7" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="M7" s="19" t="s">
+      <c r="M7" s="18" t="s">
         <v>24</v>
       </c>
-      <c r="N7" s="22" t="s">
+      <c r="N7" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="O7" s="11" t="s">
+      <c r="O7" s="10" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="8" spans="1:17" ht="15">
+    <row r="8" spans="1:15" ht="15" x14ac:dyDescent="0.25">
       <c r="F8" s="1" t="s">
         <v>57</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="M8" s="19" t="s">
+      <c r="M8" s="18" t="s">
         <v>27</v>
       </c>
-      <c r="N8" s="23" t="s">
+      <c r="N8" s="22" t="s">
         <v>28</v>
       </c>
-      <c r="O8" s="11" t="s">
+      <c r="O8" s="10" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="9" spans="1:17" ht="15" customHeight="1">
+    <row r="9" spans="1:15" ht="15" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F9" s="1" t="s">
         <v>58</v>
       </c>
-      <c r="M9" s="19" t="s">
+      <c r="M9" s="18" t="s">
         <v>30</v>
       </c>
-      <c r="N9" s="21" t="s">
+      <c r="N9" s="20" t="s">
         <v>33</v>
       </c>
-      <c r="O9" s="11" t="s">
+      <c r="O9" s="10" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="10" spans="1:17" ht="15">
-      <c r="M10" s="19" t="s">
+    <row r="10" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="M10" s="18" t="s">
         <v>32</v>
       </c>
-      <c r="N10" s="21" t="s">
+      <c r="N10" s="20" t="s">
         <v>34</v>
       </c>
-      <c r="O10" s="11"/>
-    </row>
-    <row r="11" spans="1:17" ht="15">
-      <c r="M11" s="19" t="s">
+      <c r="O10" s="10"/>
+    </row>
+    <row r="11" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="M11" s="18" t="s">
         <v>35</v>
       </c>
-      <c r="N11" s="21" t="s">
+      <c r="N11" s="20" t="s">
         <v>45</v>
       </c>
-      <c r="O11" s="11"/>
-    </row>
-    <row r="12" spans="1:17" ht="15">
-      <c r="M12" s="13" t="s">
+      <c r="O11" s="10"/>
+    </row>
+    <row r="12" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="M12" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="N12" s="24" t="s">
+      <c r="N12" s="23" t="s">
         <v>46</v>
       </c>
-      <c r="O12" s="25" t="s">
+      <c r="O12" s="24" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="13" spans="1:17" ht="15">
-      <c r="M13" s="19" t="s">
+    <row r="13" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="M13" s="18" t="s">
         <v>38</v>
       </c>
-      <c r="N13" s="21" t="s">
+      <c r="N13" s="20" t="s">
         <v>50</v>
       </c>
-      <c r="O13" s="11" t="s">
+      <c r="O13" s="10" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="14" spans="1:17" ht="15">
-      <c r="M14" s="19" t="s">
+    <row r="14" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="M14" s="18" t="s">
         <v>39</v>
       </c>
       <c r="N14" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="O14" s="11" t="s">
+      <c r="O14" s="10" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="15" spans="1:17" ht="15">
-      <c r="M15" s="19" t="s">
+    <row r="15" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="M15" s="18" t="s">
         <v>41</v>
       </c>
       <c r="N15" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="O15" s="11" t="s">
+      <c r="O15" s="10" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="16" spans="1:17" ht="15">
-      <c r="M16" s="13" t="s">
+    <row r="16" spans="1:15" ht="15" x14ac:dyDescent="0.25">
+      <c r="M16" s="12" t="s">
         <v>43</v>
       </c>
-      <c r="N16" s="24" t="s">
+      <c r="N16" s="23" t="s">
         <v>49</v>
       </c>
-      <c r="O16" s="25" t="s">
+      <c r="O16" s="24" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="19" spans="14:14">
+    <row r="19" spans="14:14" x14ac:dyDescent="0.2">
       <c r="N19" s="1" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="20" spans="14:14">
+    <row r="20" spans="14:14" x14ac:dyDescent="0.2">
       <c r="N20" s="1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="21" spans="14:14">
-      <c r="N21" s="20" t="s">
+    <row r="21" spans="14:14" x14ac:dyDescent="0.2">
+      <c r="N21" s="19" t="s">
         <v>35</v>
       </c>
     </row>
@@ -2067,18 +2571,18 @@
     <mergeCell ref="M1:O1"/>
   </mergeCells>
   <dataValidations count="3">
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="J5">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="J5" xr:uid="{00000000-0002-0000-0700-000000000000}">
       <formula1>$J$7:$J$8</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="N12">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="N12" xr:uid="{00000000-0002-0000-0700-000001000000}">
       <formula1>$N$19:$N$21</formula1>
     </dataValidation>
-    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="F5">
+    <dataValidation type="list" showInputMessage="1" showErrorMessage="1" sqref="F5" xr:uid="{00000000-0002-0000-0700-000002000000}">
       <formula1>$F$7:$F$9</formula1>
     </dataValidation>
   </dataValidations>
   <hyperlinks>
-    <hyperlink ref="N7" r:id="rId1"/>
+    <hyperlink ref="N7" r:id="rId1" xr:uid="{00000000-0004-0000-0700-000000000000}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="1200" verticalDpi="1200" r:id="rId2"/>
